--- a/ValueSet-mii-vs-pro-bdi-bdi2-long.xlsx
+++ b/ValueSet-mii-vs-pro-bdi-bdi2-long.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.rc4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T17:47:08+00:00</t>
+    <t>2026-09-08T17:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-pro-bdi-bdi2-long.xlsx
+++ b/ValueSet-mii-vs-pro-bdi-bdi2-long.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc4</t>
+    <t>2027.0.0-ballot.rc5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T17:30:22+00:00</t>
+    <t>2026-09-11T10:35:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-pro-bdi-bdi2-long.xlsx
+++ b/ValueSet-mii-vs-pro-bdi-bdi2-long.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc5</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:35:27+00:00</t>
+    <t>2026-09-11T13:28:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-pro-bdi-bdi2-long.xlsx
+++ b/ValueSet-mii-vs-pro-bdi-bdi2-long.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T13:28:57+00:00</t>
+    <t>2026-09-11T16:14:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
